--- a/generated/spreadsheet/verbose/full-planning-permission-full-verbose.xlsx
+++ b/generated/spreadsheet/verbose/full-planning-permission-full-verbose.xlsx
@@ -1024,7 +1024,7 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Planning requirement references identifying the information this document provides. A document may address more than one requirement. These references identify its coverage; they do not establish that the requirements have been satisfied.</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Planning officer name</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
@@ -8103,12 +8103,12 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>unit-type</t>
+          <t>capacity-unit</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Capacity unit</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr"/>
@@ -8117,7 +8117,7 @@
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Unit used to express the total capacity of a waste management facility</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
@@ -8201,12 +8201,12 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>unit-type</t>
+          <t>throughput-unit</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Throughput unit</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr"/>
@@ -8215,7 +8215,7 @@
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Unit used to express the annual throughput of a waste management facility</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
@@ -8459,7 +8459,7 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>A description of the development, works, change of use or reserved matters for which approval is sought</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
